--- a/src/nodes/HPC/compressor_stage_7_blade_stator_coordinates_lattice.xlsx
+++ b/src/nodes/HPC/compressor_stage_7_blade_stator_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>5.9931218899714844</v>
+        <v>5.5741261866238023</v>
       </c>
       <c r="B1">
-        <v>8.1575457417232737</v>
+        <v>8.4493893135514639</v>
       </c>
       <c r="C1">
         <v>194.11826296981104</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>5.3740951986233778</v>
+        <v>4.9642088538298772</v>
       </c>
       <c r="B2">
-        <v>7.9925238198663235</v>
+        <v>8.2533609317995111</v>
       </c>
       <c r="C2">
         <v>194.11826296981104</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>4.8172637825420406</v>
+        <v>4.41953603532229</v>
       </c>
       <c r="B3">
-        <v>7.7654657934770146</v>
+        <v>7.9985117723699455</v>
       </c>
       <c r="C3">
         <v>194.11826296981104</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>4.2758818544849646</v>
+        <v>3.8910701447170535</v>
       </c>
       <c r="B4">
-        <v>7.5229978175387471</v>
+        <v>7.7290513599728481</v>
       </c>
       <c r="C4">
         <v>194.11826296981104</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>3.7472245151943677</v>
+        <v>3.3759526895034369</v>
       </c>
       <c r="B5">
-        <v>7.2678378177214507</v>
+        <v>7.4475567503853419</v>
       </c>
       <c r="C5">
         <v>194.11826296981104</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>3.2301116897649984</v>
+        <v>2.8729457394096527</v>
       </c>
       <c r="B6">
-        <v>7.00116284887156</v>
+        <v>7.1551439917854722</v>
       </c>
       <c r="C6">
         <v>194.11826296981104</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>2.7238293916791996</v>
+        <v>2.3813003034013884</v>
       </c>
       <c r="B7">
-        <v>6.7236850702657112</v>
+        <v>6.8524883322855761</v>
       </c>
       <c r="C7">
         <v>194.11826296981104</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>2.227918065642863</v>
+        <v>1.9005342956317173</v>
       </c>
       <c r="B8">
-        <v>6.4358628610997757</v>
+        <v>6.540024393320631</v>
       </c>
       <c r="C8">
         <v>194.11826296981104</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>1.7417313261211638</v>
+        <v>1.4299696403130398</v>
       </c>
       <c r="B9">
-        <v>6.1383409526726274</v>
+        <v>6.218363489812468</v>
       </c>
       <c r="C9">
         <v>194.11826296981104</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>1.264584593807772</v>
+        <v>0.9688881953655889</v>
       </c>
       <c r="B10">
-        <v>5.8318021723087838</v>
+        <v>5.8881530581942787</v>
       </c>
       <c r="C10">
         <v>194.11826296981104</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>0.795827344551059</v>
+        <v>0.51660754348157578</v>
       </c>
       <c r="B11">
-        <v>5.51689537933234</v>
+        <v>5.5500083274578653</v>
       </c>
       <c r="C11">
         <v>194.11826296981104</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>0.3350823587709873</v>
+        <v>0.072731971189628639</v>
       </c>
       <c r="B12">
-        <v>5.1939968279394266</v>
+        <v>5.2042860505713184</v>
       </c>
       <c r="C12">
         <v>194.11826296981104</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-0.11696841998079868</v>
+        <v>-0.3620231444079417</v>
       </c>
       <c r="B13">
-        <v>4.8624263198147624</v>
+        <v>4.8503412838493256</v>
       </c>
       <c r="C13">
         <v>194.11826296981104</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-0.5599364337619166</v>
+        <v>-0.78725019559312193</v>
       </c>
       <c r="B14">
-        <v>4.5217962914171146</v>
+        <v>4.4878065511412331</v>
       </c>
       <c r="C14">
         <v>194.11826296981104</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-0.99566583019871091</v>
+        <v>-1.2048837427587542</v>
       </c>
       <c r="B15">
-        <v>4.1739461708128447</v>
+        <v>4.1184259430884689</v>
       </c>
       <c r="C15">
         <v>194.11826296981104</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-1.4258477264780893</v>
+        <v>-1.6166978132563998</v>
       </c>
       <c r="B16">
-        <v>3.8205627472658255</v>
+        <v>3.7437988227881722</v>
       </c>
       <c r="C16">
         <v>194.11826296981104</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-1.8493284124605063</v>
+        <v>-2.0214821341616442</v>
       </c>
       <c r="B17">
-        <v>3.4604952632223682</v>
+        <v>3.3628340763682387</v>
       </c>
       <c r="C17">
         <v>194.11826296981104</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-2.264602824084569</v>
+        <v>-2.4176578528488788</v>
       </c>
       <c r="B18">
-        <v>3.0922425063952059</v>
+        <v>2.9741082992667325</v>
       </c>
       <c r="C18">
         <v>194.11826296981104</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-2.6716053089279659</v>
+        <v>-2.8051560981637103</v>
       </c>
       <c r="B19">
-        <v>2.7157389923803272</v>
+        <v>2.5775594011316123</v>
       </c>
       <c r="C19">
         <v>194.11826296981104</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-3.07063006747816</v>
+        <v>-3.1842854943195524</v>
       </c>
       <c r="B20">
-        <v>2.3312781687445319</v>
+        <v>2.1734656201633062</v>
       </c>
       <c r="C20">
         <v>194.11826296981104</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-3.4619713002226074</v>
+        <v>-3.5553546655298156</v>
       </c>
       <c r="B21">
-        <v>1.9391534830546218</v>
+        <v>1.7621051945622481</v>
       </c>
       <c r="C21">
         <v>194.11826296981104</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-3.8458689372377819</v>
+        <v>-3.918615304889109</v>
       </c>
       <c r="B22">
-        <v>1.5396042513557522</v>
+        <v>1.343705036640112</v>
       </c>
       <c r="C22">
         <v>194.11826296981104</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-4.2223458269561833</v>
+        <v>-4.2740913810168246</v>
       </c>
       <c r="B23">
-        <v>1.1326532636065034</v>
+        <v>0.91828675515355762</v>
       </c>
       <c r="C23">
         <v>194.11826296981104</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-4.5913705473993245</v>
+        <v>-4.6217499314135519</v>
       </c>
       <c r="B24">
-        <v>0.71826917824381087</v>
+        <v>0.4858206329704895</v>
       </c>
       <c r="C24">
         <v>194.11826296981104</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-4.952911676588716</v>
+        <v>-4.9615579935798753</v>
       </c>
       <c r="B25">
-        <v>0.2964206537046099</v>
+        <v>0.0462769529588113</v>
       </c>
       <c r="C25">
         <v>194.11826296981104</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-5.3069253737697366</v>
+        <v>-5.29346957738666</v>
       </c>
       <c r="B26">
-        <v>-0.13293603856805039</v>
+        <v>-0.40038574699045265</v>
       </c>
       <c r="C26">
         <v>194.11826296981104</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-5.6533181230832232</v>
+        <v>-5.617386582185862</v>
       </c>
       <c r="B27">
-        <v>-0.5698941751066644</v>
+        <v>-0.85425590889379788</v>
       </c>
       <c r="C27">
         <v>194.11826296981104</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-5.9919839898938836</v>
+        <v>-5.9331978796997067</v>
       </c>
       <c r="B28">
-        <v>-1.014559419437608</v>
+        <v>-1.3154337197445969</v>
       </c>
       <c r="C28">
         <v>194.11826296981104</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-6.3228170395664218</v>
+        <v>-6.2407923416504243</v>
       </c>
       <c r="B29">
-        <v>-1.4670374350872615</v>
+        <v>-1.7840193665362254</v>
       </c>
       <c r="C29">
         <v>194.11826296981104</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-6.6457440299617438</v>
+        <v>-6.5400931350668605</v>
       </c>
       <c r="B30">
-        <v>-1.927401276752748</v>
+        <v>-2.2600821175460872</v>
       </c>
       <c r="C30">
         <v>194.11826296981104</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-6.9608224889255546</v>
+        <v>-6.8311606082043275</v>
       </c>
       <c r="B31">
-        <v>-2.3955935638141561</v>
+        <v>-2.7435675661876888</v>
       </c>
       <c r="C31">
         <v>194.11826296981104</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-7.2681426367997712</v>
+        <v>-7.1140894046247647</v>
       </c>
       <c r="B32">
-        <v>-2.8715243068223359</v>
+        <v>-3.2343903871585882</v>
       </c>
       <c r="C32">
         <v>194.11826296981104</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-7.5677946939262979</v>
+        <v>-7.3889741678901011</v>
       </c>
       <c r="B33">
-        <v>-3.3551035163281173</v>
+        <v>-3.7324652551563182</v>
       </c>
       <c r="C33">
         <v>194.11826296981104</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-7.8598028550702983</v>
+        <v>-7.6558402789588493</v>
       </c>
       <c r="B34">
-        <v>-3.846307059485818</v>
+        <v>-4.23776928813886</v>
       </c>
       <c r="C34">
         <v>194.11826296981104</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-8.14392721268993</v>
+        <v>-7.91443606837583</v>
       </c>
       <c r="B35">
-        <v>-4.3453742298636309</v>
+        <v>-4.7505293771059067</v>
       </c>
       <c r="C35">
         <v>194.11826296981104</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-8.419861833666598</v>
+        <v>-8.1644406040824418</v>
       </c>
       <c r="B36">
-        <v>-4.8526101776332311</v>
+        <v>-5.27103485631759</v>
       </c>
       <c r="C36">
         <v>194.11826296981104</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-8.6873007848817174</v>
+        <v>-8.4055329540200887</v>
       </c>
       <c r="B37">
-        <v>-5.3683200529662916</v>
+        <v>-5.79957506003404</v>
       </c>
       <c r="C37">
         <v>194.11826296981104</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-8.94578396737804</v>
+        <v>-8.6372304620246059</v>
       </c>
       <c r="B38">
-        <v>-5.89296277733047</v>
+        <v>-6.3365851238561177</v>
       </c>
       <c r="C38">
         <v>194.11826296981104</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-9.1942346188436961</v>
+        <v>-8.8584035755095911</v>
       </c>
       <c r="B39">
-        <v>-6.427612357377388</v>
+        <v>-6.88308338874761</v>
       </c>
       <c r="C39">
         <v>194.11826296981104</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-9.4314218111281569</v>
+        <v>-9.0677610177830719</v>
       </c>
       <c r="B40">
-        <v>-6.973496571054647</v>
+        <v>-7.440233997013034</v>
       </c>
       <c r="C40">
         <v>194.11826296981104</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-9.6561146160808988</v>
+        <v>-9.2640115121530862</v>
       </c>
       <c r="B41">
-        <v>-7.5318431963098558</v>
+        <v>-8.0092010909569069</v>
       </c>
       <c r="C41">
         <v>194.11826296981104</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-9.6561146160808988</v>
+        <v>-9.2640115121530862</v>
       </c>
       <c r="B42">
-        <v>-7.5318431963098558</v>
+        <v>-8.0092010909569069</v>
       </c>
       <c r="C42">
         <v>194.11826296981104</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-9.3797777065540728</v>
+        <v>-9.0135849649521056</v>
       </c>
       <c r="B43">
-        <v>-7.0250085075497637</v>
+        <v>-7.4890760735290085</v>
       </c>
       <c r="C43">
         <v>194.11826296981104</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-9.0998158762146115</v>
+        <v>-8.7593557784552587</v>
       </c>
       <c r="B44">
-        <v>-6.5217894626708111</v>
+        <v>-6.9723793014188491</v>
       </c>
       <c r="C44">
         <v>194.11826296981104</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-8.8152742663815591</v>
+        <v>-8.500322280259228</v>
       </c>
       <c r="B45">
-        <v>-6.0231384766706215</v>
+        <v>-6.4600138260229434</v>
       </c>
       <c r="C45">
         <v>194.11826296981104</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-8.52519801837396</v>
+        <v>-8.2354827979607084</v>
       </c>
       <c r="B46">
-        <v>-5.5300079645468241</v>
+        <v>-5.9528826987378025</v>
       </c>
       <c r="C46">
         <v>194.11826296981104</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-8.2287737840125263</v>
+        <v>-7.9639841074735322</v>
       </c>
       <c r="B47">
-        <v>-5.0432091929503784</v>
+        <v>-5.4517551383219764</v>
       </c>
       <c r="C47">
         <v>194.11826296981104</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-7.9257542571246624</v>
+        <v>-7.6855667779801333</v>
       </c>
       <c r="B48">
-        <v>-4.5629888351455961</v>
+        <v>-4.9568650329821509</v>
       </c>
       <c r="C48">
         <v>194.11826296981104</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-7.61603364203944</v>
+        <v>-7.4001198269800978</v>
       </c>
       <c r="B49">
-        <v>-4.0894524160501273</v>
+        <v>-4.4683124382870529</v>
       </c>
       <c r="C49">
         <v>194.11826296981104</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-7.2995061430859307</v>
+        <v>-7.1075322719730076</v>
       </c>
       <c r="B50">
-        <v>-3.6227054605816131</v>
+        <v>-3.9861974098054036</v>
       </c>
       <c r="C50">
         <v>194.11826296981104</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-6.9761204629413465</v>
+        <v>-6.8077503006894347</v>
       </c>
       <c r="B51">
-        <v>-3.1627991347822668</v>
+        <v>-3.5105684616471082</v>
       </c>
       <c r="C51">
         <v>194.11826296981104</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-6.6460432976754111</v>
+        <v>-6.50094878178389</v>
       </c>
       <c r="B52">
-        <v>-2.7095671691925016</v>
+        <v>-3.041267942086765</v>
       </c>
       <c r="C52">
         <v>194.11826296981104</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-6.309495841705993</v>
+        <v>-6.1873597541418794</v>
       </c>
       <c r="B53">
-        <v>-2.2627889354773036</v>
+        <v>-2.5780866579401609</v>
       </c>
       <c r="C53">
         <v>194.11826296981104</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-5.9666992894509461</v>
+        <v>-5.8672152566488931</v>
       </c>
       <c r="B54">
-        <v>-1.8222438053016385</v>
+        <v>-2.1208154160230634</v>
       </c>
       <c r="C54">
         <v>194.11826296981104</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-5.6178328365262695</v>
+        <v>-5.5407032703192129</v>
       </c>
       <c r="B55">
-        <v>-1.3877530416486252</v>
+        <v>-1.6692847432453768</v>
       </c>
       <c r="C55">
         <v>194.11826296981104</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-5.2629076833404911</v>
+        <v>-5.20783554468222</v>
       </c>
       <c r="B56">
-        <v>-0.95930547277393041</v>
+        <v>-1.2234840468934747</v>
       </c>
       <c r="C56">
         <v>194.11826296981104</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-4.9018930315002667</v>
+        <v>-4.8685797713960683</v>
       </c>
       <c r="B57">
-        <v>-0.53693181825135339</v>
+        <v>-0.78344245434784809</v>
       </c>
       <c r="C57">
         <v>194.11826296981104</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-4.5347580826122575</v>
+        <v>-4.5229036421189184</v>
       </c>
       <c r="B58">
-        <v>-0.12066279765469805</v>
+        <v>-0.34918909298899</v>
       </c>
       <c r="C58">
         <v>194.11826296981104</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.1614760639509534</v>
+        <v>-4.1707790715426087</v>
       </c>
       <c r="B59">
-        <v>0.28947488480753764</v>
+        <v>0.079250717051815384</v>
       </c>
       <c r="C59">
         <v>194.11826296981104</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-3.7820363054621753</v>
+        <v>-3.812194866493714</v>
       </c>
       <c r="B60">
-        <v>0.69347058638808112</v>
+        <v>0.50186688464012386</v>
       </c>
       <c r="C60">
         <v>194.11826296981104</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-3.396432162759579</v>
+        <v>-3.4471440568324931</v>
       </c>
       <c r="B61">
-        <v>1.0913176797049604</v>
+        <v>0.91865312589069759</v>
       </c>
       <c r="C61">
         <v>194.11826296981104</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-3.0046569914568182</v>
+        <v>-3.0756196724192053</v>
       </c>
       <c r="B62">
-        <v>1.4830095373762069</v>
+        <v>1.3296031569182996</v>
       </c>
       <c r="C62">
         <v>194.11826296981104</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-2.6067499848519589</v>
+        <v>-2.6976628280762327</v>
       </c>
       <c r="B63">
-        <v>1.868585252396026</v>
+        <v>1.7347540445300458</v>
       </c>
       <c r="C63">
         <v>194.11826296981104</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-2.2029336869807077</v>
+        <v>-2.3135069784744426</v>
       </c>
       <c r="B64">
-        <v>2.2482667992633356</v>
+        <v>2.1343162583024742</v>
       </c>
       <c r="C64">
         <v>194.11826296981104</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.7934764795631866</v>
+        <v>-1.923433663246833</v>
       </c>
       <c r="B65">
-        <v>2.6223218728532278</v>
+        <v>2.5285436185044725</v>
       </c>
       <c r="C65">
         <v>194.11826296981104</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-1.3786467443195121</v>
+        <v>-1.5277244220263933</v>
       </c>
       <c r="B66">
-        <v>2.9910181680407968</v>
+        <v>2.9176899454049323</v>
       </c>
       <c r="C66">
         <v>194.11826296981104</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-0.958346071741773</v>
+        <v>-1.1262760205960978</v>
       </c>
       <c r="B67">
-        <v>3.3542575271686674</v>
+        <v>3.3016621688508305</v>
       </c>
       <c r="C67">
         <v>194.11826296981104</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-0.53100888740992169</v>
+        <v>-0.717446129338834</v>
       </c>
       <c r="B68">
-        <v>3.7104783824495966</v>
+        <v>3.6789796570014928</v>
       </c>
       <c r="C68">
         <v>194.11826296981104</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-0.095410723588764623</v>
+        <v>-0.29995024871184234</v>
       </c>
       <c r="B69">
-        <v>4.0584593998177576</v>
+        <v>4.04848437744825</v>
       </c>
       <c r="C69">
         <v>194.11826296981104</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>0.3468412958053369</v>
+        <v>0.12452570513013474</v>
       </c>
       <c r="B70">
-        <v>4.3998035902228416</v>
+        <v>4.4116962571980833</v>
       </c>
       <c r="C70">
         <v>194.11826296981104</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>0.79399531093907139</v>
+        <v>0.55414398416794419</v>
       </c>
       <c r="B71">
-        <v>4.7362583301219727</v>
+        <v>4.7702721063114923</v>
       </c>
       <c r="C71">
         <v>194.11826296981104</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>1.2465521099628751</v>
+        <v>0.98942992862229273</v>
       </c>
       <c r="B72">
-        <v>5.0673241129864675</v>
+        <v>5.1237383076474012</v>
       </c>
       <c r="C72">
         <v>194.11826296981104</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>1.70531586600603</v>
+        <v>1.4312271377054535</v>
       </c>
       <c r="B73">
-        <v>5.3921988237344882</v>
+        <v>5.4713343196912163</v>
       </c>
       <c r="C73">
         <v>194.11826296981104</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>2.1700516441294684</v>
+        <v>1.8792891583561184</v>
       </c>
       <c r="B74">
-        <v>5.7111167960573974</v>
+        <v>5.8132823306358583</v>
       </c>
       <c r="C74">
         <v>194.11826296981104</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>2.6402617474745238</v>
+        <v>2.3330938932016796</v>
       </c>
       <c r="B75">
-        <v>6.0245744531033685</v>
+        <v>6.1500530340532853</v>
       </c>
       <c r="C75">
         <v>194.11826296981104</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>3.1154365395725065</v>
+        <v>2.7921067198979173</v>
       </c>
       <c r="B76">
-        <v>6.333080127074644</v>
+        <v>6.4821284153241052</v>
       </c>
       <c r="C76">
         <v>194.11826296981104</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>3.5951165723886311</v>
+        <v>3.2558456651158187</v>
       </c>
       <c r="B77">
-        <v>6.637092090182267</v>
+        <v>6.8099429944434871</v>
       </c>
       <c r="C77">
         <v>194.11826296981104</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>4.0790550912337684</v>
+        <v>3.7240518765587889</v>
       </c>
       <c r="B78">
-        <v>6.9368564656184422</v>
+        <v>7.13373013805621</v>
       </c>
       <c r="C78">
         <v>194.11826296981104</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>4.5667631253960979</v>
+        <v>4.1962124108166385</v>
       </c>
       <c r="B79">
-        <v>7.2328609727165354</v>
+        <v>7.4539522870375245</v>
       </c>
       <c r="C79">
         <v>194.11826296981104</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>5.0573114332939477</v>
+        <v>4.6713524685112677</v>
       </c>
       <c r="B80">
-        <v>7.5260324749344143</v>
+        <v>7.77148826557866</v>
       </c>
       <c r="C80">
         <v>194.11826296981104</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>5.5482474158355455</v>
+        <v>5.14689920731992</v>
       </c>
       <c r="B81">
-        <v>7.8188172946491425</v>
+        <v>8.088657603343087</v>
       </c>
       <c r="C81">
         <v>194.11826296981104</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>5.9931218899714844</v>
+        <v>5.5741261866238023</v>
       </c>
       <c r="B82">
-        <v>8.1575457417232737</v>
+        <v>8.4493893135514639</v>
       </c>
       <c r="C82">
         <v>194.11826296981104</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>6.2380833917444924</v>
+        <v>5.7659341549007674</v>
       </c>
       <c r="B1">
-        <v>9.288739315425282</v>
+        <v>9.58897104978603</v>
       </c>
       <c r="C1">
         <v>216.89590882303355</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>5.4928100005274541</v>
+        <v>4.994070079665641</v>
       </c>
       <c r="B2">
-        <v>9.1427224760786547</v>
+        <v>9.4348555761120743</v>
       </c>
       <c r="C2">
         <v>216.89590882303355</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>4.8605626461496847</v>
+        <v>4.3619378299650551</v>
       </c>
       <c r="B3">
-        <v>8.8926658459616057</v>
+        <v>9.1644688575687354</v>
       </c>
       <c r="C3">
         <v>216.89590882303355</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>4.2519826448288516</v>
+        <v>3.7575440504354423</v>
       </c>
       <c r="B4">
-        <v>8.6208235589375981</v>
+        <v>8.871000880012188</v>
       </c>
       <c r="C4">
         <v>216.89590882303355</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>3.661951748200956</v>
+        <v>3.1745061225386126</v>
       </c>
       <c r="B5">
-        <v>8.3319069320075041</v>
+        <v>8.5597626382721543</v>
       </c>
       <c r="C5">
         <v>216.89590882303355</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>3.0883007440168626</v>
+        <v>2.6101359668675581</v>
       </c>
       <c r="B6">
-        <v>8.0279127120700675</v>
+        <v>8.2329908907804761</v>
       </c>
       <c r="C6">
         <v>216.89590882303355</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>2.529743375092409</v>
+        <v>2.0628492130116793</v>
       </c>
       <c r="B7">
-        <v>7.7100248911687146</v>
+        <v>7.8920039966101054</v>
       </c>
       <c r="C7">
         <v>216.89590882303355</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>1.9854760243902505</v>
+        <v>1.5316650417584294</v>
       </c>
       <c r="B8">
-        <v>7.37898319397895</v>
+        <v>7.5376180981852867</v>
       </c>
       <c r="C8">
         <v>216.89590882303355</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>1.4543283881982088</v>
+        <v>1.0151396469230971</v>
       </c>
       <c r="B9">
-        <v>7.0358648780668895</v>
+        <v>7.1710345906914279</v>
       </c>
       <c r="C9">
         <v>216.89590882303355</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>0.93505282441425</v>
+        <v>0.51173074967592735</v>
       </c>
       <c r="B10">
-        <v>6.6818183905238557</v>
+        <v>6.793536808678736</v>
       </c>
       <c r="C10">
         <v>216.89590882303355</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>0.42645902405177027</v>
+        <v>0.019965167579131388</v>
       </c>
       <c r="B11">
-        <v>6.3179394036513941</v>
+        <v>6.4063505913954</v>
       </c>
       <c r="C11">
         <v>216.89590882303355</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-0.072124006148921879</v>
+        <v>-0.46098053128459415</v>
       </c>
       <c r="B12">
-        <v>5.9448455627310617</v>
+        <v>6.0101611188548</v>
       </c>
       <c r="C12">
         <v>216.89590882303355</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-0.55934732965529388</v>
+        <v>-0.92939987314256178</v>
       </c>
       <c r="B13">
-        <v>5.56129517975422</v>
+        <v>5.6035484294331068</v>
       </c>
       <c r="C13">
         <v>216.89590882303355</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-1.0344270691533333</v>
+        <v>-1.384296063844072</v>
       </c>
       <c r="B14">
-        <v>5.1665667003426039</v>
+        <v>5.1856830879151374</v>
       </c>
       <c r="C14">
         <v>216.89590882303355</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-1.5008595139953442</v>
+        <v>-1.8300409334163821</v>
       </c>
       <c r="B15">
-        <v>4.7638784379296331</v>
+        <v>4.7602029063575308</v>
       </c>
       <c r="C15">
         <v>216.89590882303355</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-1.9618510435495205</v>
+        <v>-2.2706438850704131</v>
       </c>
       <c r="B16">
-        <v>4.356181845542654</v>
+        <v>4.3304441204441373</v>
       </c>
       <c r="C16">
         <v>216.89590882303355</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.4151682305813535</v>
+        <v>-2.7032959905738396</v>
       </c>
       <c r="B17">
-        <v>3.9414210667730183</v>
+        <v>3.8940694130958122</v>
       </c>
       <c r="C17">
         <v>216.89590882303355</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-2.8579088881335908</v>
+        <v>-3.1243511659859577</v>
       </c>
       <c r="B18">
-        <v>3.516924655887935</v>
+        <v>3.4480448676148985</v>
       </c>
       <c r="C18">
         <v>216.89590882303355</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-3.2899355969607247</v>
+        <v>-3.533633035975833</v>
       </c>
       <c r="B19">
-        <v>3.0825661192939786</v>
+        <v>2.992223721592663</v>
       </c>
       <c r="C19">
         <v>216.89590882303355</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-3.7118021297451884</v>
+        <v>-3.9318326523649656</v>
       </c>
       <c r="B20">
-        <v>2.6388552014325675</v>
+        <v>2.527181001192599</v>
       </c>
       <c r="C20">
         <v>216.89590882303355</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-4.1240622591694152</v>
+        <v>-4.3196410669748611</v>
       </c>
       <c r="B21">
-        <v>2.1863016467451262</v>
+        <v>2.0534917325782041</v>
       </c>
       <c r="C21">
         <v>216.89590882303355</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-4.5271689241871576</v>
+        <v>-4.6976239672489024</v>
       </c>
       <c r="B22">
-        <v>1.725322382829027</v>
+        <v>1.5716266258614904</v>
       </c>
       <c r="C22">
         <v>216.89590882303355</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-4.9211717288374572</v>
+        <v>-5.065845583117996</v>
       </c>
       <c r="B23">
-        <v>1.2559630699054678</v>
+        <v>1.0816391269485413</v>
       </c>
       <c r="C23">
         <v>216.89590882303355</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-5.3060194434306762</v>
+        <v>-5.4242447801349236</v>
       </c>
       <c r="B24">
-        <v>0.77817655135160479</v>
+        <v>0.58347836569395617</v>
       </c>
       <c r="C24">
         <v>216.89590882303355</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-5.6816608382771765</v>
+        <v>-5.7727604238524748</v>
       </c>
       <c r="B25">
-        <v>0.29191567054458667</v>
+        <v>0.077093471952333417</v>
       </c>
       <c r="C25">
         <v>216.89590882303355</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-6.0480239282655361</v>
+        <v>-6.1113064071803835</v>
       </c>
       <c r="B26">
-        <v>-0.20288583438001678</v>
+        <v>-0.43758720422821346</v>
       </c>
       <c r="C26">
         <v>216.89590882303355</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-6.4049537065972</v>
+        <v>-6.4396967324561878</v>
       </c>
       <c r="B27">
-        <v>-0.70637064625300472</v>
+        <v>-0.96071843202553531</v>
       </c>
       <c r="C27">
         <v>216.89590882303355</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-6.7522744110518325</v>
+        <v>-6.7577204293743787</v>
       </c>
       <c r="B28">
-        <v>-1.2187005531467645</v>
+        <v>-1.4924757604239725</v>
       </c>
       <c r="C28">
         <v>216.89590882303355</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-7.0898102794090887</v>
+        <v>-7.0651665276294446</v>
       </c>
       <c r="B29">
-        <v>-1.7400373431336766</v>
+        <v>-2.0330347384078609</v>
       </c>
       <c r="C29">
         <v>216.89590882303355</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-7.4174514429427711</v>
+        <v>-7.3619078348100118</v>
       </c>
       <c r="B30">
-        <v>-2.2704821497189567</v>
+        <v>-2.5825012031402914</v>
       </c>
       <c r="C30">
         <v>216.89590882303355</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-7.7353516069032509</v>
+        <v>-7.6481522700812663</v>
       </c>
       <c r="B31">
-        <v>-2.8098934881391169</v>
+        <v>-3.140702144499361</v>
       </c>
       <c r="C31">
         <v>216.89590882303355</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-8.04373037003505</v>
+        <v>-7.9241915305025419</v>
       </c>
       <c r="B32">
-        <v>-3.3580692190635197</v>
+        <v>-3.7073948405419377</v>
       </c>
       <c r="C32">
         <v>216.89590882303355</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-8.3428073310826836</v>
+        <v>-8.1903173131331641</v>
       </c>
       <c r="B33">
-        <v>-3.914807203161506</v>
+        <v>-4.2823365693248716</v>
       </c>
       <c r="C33">
         <v>216.89590882303355</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-8.6326798116979866</v>
+        <v>-8.4466694651887764</v>
       </c>
       <c r="B34">
-        <v>-4.4800178564347517</v>
+        <v>-4.8654109635868572</v>
       </c>
       <c r="C34">
         <v>216.89590882303355</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-8.9129560251621154</v>
+        <v>-8.6927804345103024</v>
       </c>
       <c r="B35">
-        <v>-5.05406181621422</v>
+        <v>-5.4570070747939381</v>
       </c>
       <c r="C35">
         <v>216.89590882303355</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-9.1831219076635513</v>
+        <v>-8.9280308190949835</v>
       </c>
       <c r="B36">
-        <v>-5.6374122751632045</v>
+        <v>-6.0576403090939976</v>
       </c>
       <c r="C36">
         <v>216.89590882303355</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-9.4426633953907686</v>
+        <v>-9.1518012169400613</v>
       </c>
       <c r="B37">
-        <v>-6.2305424259450017</v>
+        <v>-6.6678260726349228</v>
       </c>
       <c r="C37">
         <v>216.89590882303355</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-9.6907758195171851</v>
+        <v>-9.3631094909835273</v>
       </c>
       <c r="B38">
-        <v>-6.834192961400821</v>
+        <v>-7.288381604427185</v>
       </c>
       <c r="C38">
         <v>216.89590882303355</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-9.9254920911559541</v>
+        <v>-9.5595225639263877</v>
       </c>
       <c r="B39">
-        <v>-7.4501745750835546</v>
+        <v>-7.92133147493163</v>
       </c>
       <c r="C39">
         <v>216.89590882303355</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-10.144554516405174</v>
+        <v>-9.7382446234104041</v>
       </c>
       <c r="B40">
-        <v>-8.0805654607240189</v>
+        <v>-8.5690020874717039</v>
       </c>
       <c r="C40">
         <v>216.89590882303355</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-10.345705401362935</v>
+        <v>-9.8964798570773347</v>
       </c>
       <c r="B41">
-        <v>-8.7274438120530213</v>
+        <v>-9.23371984537084</v>
       </c>
       <c r="C41">
         <v>216.89590882303355</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-10.345705401362935</v>
+        <v>-9.8964798570773347</v>
       </c>
       <c r="B42">
-        <v>-8.7274438120530213</v>
+        <v>-9.23371984537084</v>
       </c>
       <c r="C42">
         <v>216.89590882303355</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-10.045715990450237</v>
+        <v>-9.614328896571779</v>
       </c>
       <c r="B43">
-        <v>-8.1715457325974086</v>
+        <v>-8.6721127121508328</v>
       </c>
       <c r="C43">
         <v>216.89590882303355</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-9.7447897743873462</v>
+        <v>-9.33297265631228</v>
       </c>
       <c r="B44">
-        <v>-7.6165099766784214</v>
+        <v>-8.1098442899798</v>
       </c>
       <c r="C44">
         <v>216.89590882303355</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-9.4410012019554177</v>
+        <v>-9.0499623352366125</v>
       </c>
       <c r="B45">
-        <v>-7.06410900267406</v>
+        <v>-7.5489522331061893</v>
       </c>
       <c r="C45">
         <v>216.89590882303355</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-9.1324247219355925</v>
+        <v>-8.7628491322825379</v>
       </c>
       <c r="B46">
-        <v>-6.5161152689623121</v>
+        <v>-6.9914741957784381</v>
       </c>
       <c r="C46">
         <v>216.89590882303355</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-8.8174100551457286</v>
+        <v>-8.4695309620766</v>
       </c>
       <c r="B47">
-        <v>-5.9740478476581043</v>
+        <v>-6.4391593291456095</v>
       </c>
       <c r="C47">
         <v>216.89590882303355</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-8.49540801055051</v>
+        <v>-8.16929260200041</v>
       </c>
       <c r="B48">
-        <v>-5.4384122658241</v>
+        <v>-5.892602771959246</v>
       </c>
       <c r="C48">
         <v>216.89590882303355</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-8.166144669151322</v>
+        <v>-7.861765545124352</v>
       </c>
       <c r="B49">
-        <v>-4.90946066425989</v>
+        <v>-5.3521111598714981</v>
       </c>
       <c r="C49">
         <v>216.89590882303355</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-7.8293461119495511</v>
+        <v>-7.5465812845187985</v>
       </c>
       <c r="B50">
-        <v>-4.3874451837650676</v>
+        <v>-4.8179911285345218</v>
       </c>
       <c r="C50">
         <v>216.89590882303355</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-7.4848468062989646</v>
+        <v>-7.2235086505282542</v>
       </c>
       <c r="B51">
-        <v>-3.8725181961502511</v>
+        <v>-4.2904350348685734</v>
       </c>
       <c r="C51">
         <v>216.89590882303355</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-7.1329147649628393</v>
+        <v>-6.8928658225936941</v>
       </c>
       <c r="B52">
-        <v>-3.3644329972701397</v>
+        <v>-3.7691781208662838</v>
       </c>
       <c r="C52">
         <v>216.89590882303355</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-6.7739263870568314</v>
+        <v>-6.555108317430216</v>
       </c>
       <c r="B53">
-        <v>-2.8628431139904622</v>
+        <v>-3.253841349788392</v>
       </c>
       <c r="C53">
         <v>216.89590882303355</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-6.4082580716965847</v>
+        <v>-6.2106916517529029</v>
       </c>
       <c r="B54">
-        <v>-2.367402073176931</v>
+        <v>-2.7440456848956187</v>
       </c>
       <c r="C54">
         <v>216.89590882303355</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-6.03620916433726</v>
+        <v>-5.8599759046232585</v>
       </c>
       <c r="B55">
-        <v>-1.8778343291288124</v>
+        <v>-2.2394915033885696</v>
       </c>
       <c r="C55">
         <v>216.89590882303355</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-5.6577707957920325</v>
+        <v>-5.502939404488389</v>
       </c>
       <c r="B56">
-        <v>-1.3941480458795206</v>
+        <v>-1.740196838227335</v>
       </c>
       <c r="C56">
         <v>216.89590882303355</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-5.2728570432135831</v>
+        <v>-5.1394650421418113</v>
       </c>
       <c r="B57">
-        <v>-0.91642231489601433</v>
+        <v>-1.2462591363118749</v>
       </c>
       <c r="C57">
         <v>216.89590882303355</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-4.8813819837545909</v>
+        <v>-4.7694357083770331</v>
       </c>
       <c r="B58">
-        <v>-0.44473622764524534</v>
+        <v>-0.75777584454214719</v>
       </c>
       <c r="C58">
         <v>216.89590882303355</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.4832704111719446</v>
+        <v>-4.3927487784179515</v>
       </c>
       <c r="B59">
-        <v>0.020840988975907946</v>
+        <v>-0.27483235728286304</v>
       </c>
       <c r="C59">
         <v>216.89590882303355</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-4.0784899856394041</v>
+        <v>-4.0093595652100058</v>
       </c>
       <c r="B60">
-        <v>0.48027956635084307</v>
+        <v>0.2025341412422374</v>
       </c>
       <c r="C60">
         <v>216.89590882303355</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-3.6670190839349392</v>
+        <v>-3.6192378661290121</v>
       </c>
       <c r="B61">
-        <v>0.93355960043303865</v>
+        <v>0.67429851934466589</v>
       </c>
       <c r="C61">
         <v>216.89590882303355</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-3.2488360828365197</v>
+        <v>-3.2223534785507968</v>
       </c>
       <c r="B62">
-        <v>1.3806611871759671</v>
+        <v>1.1404356453359288</v>
       </c>
       <c r="C62">
         <v>216.89590882303355</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-2.8240101162181257</v>
+        <v>-2.8187910365087139</v>
       </c>
       <c r="B63">
-        <v>1.8216479638970597</v>
+        <v>1.6010159434331241</v>
       </c>
       <c r="C63">
         <v>216.89590882303355</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-2.3929733463377874</v>
+        <v>-2.4090945206662662</v>
       </c>
       <c r="B64">
-        <v>2.2569177333695665</v>
+        <v>2.0564920614756987</v>
       </c>
       <c r="C64">
         <v>216.89590882303355</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.9562486925495457</v>
+        <v>-1.9939227483444915</v>
       </c>
       <c r="B65">
-        <v>2.6869518397306944</v>
+        <v>2.5074122032086876</v>
       </c>
       <c r="C65">
         <v>216.89590882303355</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-1.5143590742074387</v>
+        <v>-1.5739345368644271</v>
       </c>
       <c r="B66">
-        <v>3.1122316271176471</v>
+        <v>2.9543245723771259</v>
       </c>
       <c r="C66">
         <v>216.89590882303355</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.0671279223586598</v>
+        <v>-1.1489126086222192</v>
       </c>
       <c r="B67">
-        <v>3.5325945648656329</v>
+        <v>3.3970483716759943</v>
       </c>
       <c r="C67">
         <v>216.89590882303355</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-0.61158071482301479</v>
+        <v>-0.71513530631445077</v>
       </c>
       <c r="B68">
-        <v>3.94530262310185</v>
+        <v>3.8324867996000442</v>
       </c>
       <c r="C68">
         <v>216.89590882303355</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-0.14539942814114151</v>
+        <v>-0.26970531847134638</v>
       </c>
       <c r="B69">
-        <v>4.348222075098759</v>
+        <v>4.258228995129782</v>
       </c>
       <c r="C69">
         <v>216.89590882303355</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>0.32831001303556273</v>
+        <v>0.18347290334269326</v>
       </c>
       <c r="B70">
-        <v>4.7442119059178163</v>
+        <v>4.677523863388914</v>
       </c>
       <c r="C70">
         <v>216.89590882303355</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>0.806161717032806</v>
+        <v>0.64014286881216442</v>
       </c>
       <c r="B71">
-        <v>5.13638880859026</v>
+        <v>5.0939132419356747</v>
       </c>
       <c r="C71">
         <v>216.89590882303355</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>1.2890738721954322</v>
+        <v>1.1014416956512643</v>
       </c>
       <c r="B72">
-        <v>5.52390759623741</v>
+        <v>5.5064509319231858</v>
       </c>
       <c r="C72">
         <v>216.89590882303355</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>1.7785417307584592</v>
+        <v>1.5692287232658446</v>
       </c>
       <c r="B73">
-        <v>5.9053918981217741</v>
+        <v>5.9135897718044887</v>
       </c>
       <c r="C73">
         <v>216.89590882303355</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>2.2740647204984716</v>
+        <v>2.0428585697986623</v>
       </c>
       <c r="B74">
-        <v>6.2813024879805015</v>
+        <v>6.3158667856374242</v>
       </c>
       <c r="C74">
         <v>216.89590882303355</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>2.7746356397072125</v>
+        <v>2.52104935702307</v>
       </c>
       <c r="B75">
-        <v>6.6525664889607992</v>
+        <v>6.714348627898258</v>
       </c>
       <c r="C75">
         <v>216.89590882303355</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>3.2792165931955064</v>
+        <v>3.0024779424979102</v>
       </c>
       <c r="B76">
-        <v>7.0201392773754456</v>
+        <v>7.1101362891321589</v>
       </c>
       <c r="C76">
         <v>216.89590882303355</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>3.7868614967378753</v>
+        <v>3.4859347768763995</v>
       </c>
       <c r="B77">
-        <v>7.3848917180943632</v>
+        <v>7.5042362387511172</v>
       </c>
       <c r="C77">
         <v>216.89590882303355</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>4.2970222034445662</v>
+        <v>3.9707059474037489</v>
       </c>
       <c r="B78">
-        <v>7.7473283770504686</v>
+        <v>7.89724252556548</v>
       </c>
       <c r="C78">
         <v>216.89590882303355</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>4.8086827034679311</v>
+        <v>4.4554894288278586</v>
       </c>
       <c r="B79">
-        <v>8.1083844852305784</v>
+        <v>8.2902385684480411</v>
       </c>
       <c r="C79">
         <v>216.89590882303355</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>5.3199753159003818</v>
+        <v>4.9379121713568548</v>
       </c>
       <c r="B80">
-        <v>8.4697792317373661</v>
+        <v>8.6851989888022061</v>
       </c>
       <c r="C80">
         <v>216.89590882303355</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>5.8261093883858024</v>
+        <v>5.4119338175381237</v>
       </c>
       <c r="B81">
-        <v>8.8359223834061655</v>
+        <v>9.08714998504616</v>
       </c>
       <c r="C81">
         <v>216.89590882303355</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>6.2380833917444924</v>
+        <v>5.7659341549007674</v>
       </c>
       <c r="B82">
-        <v>9.288739315425282</v>
+        <v>9.58897104978603</v>
       </c>
       <c r="C82">
         <v>216.89590882303355</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>6.4355580523522447</v>
+        <v>5.911309418451733</v>
       </c>
       <c r="B1">
-        <v>10.308550377210825</v>
+        <v>10.617885105702456</v>
       </c>
       <c r="C1">
         <v>237.49899054506031</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>5.5561592883299582</v>
+        <v>4.9613608508096894</v>
       </c>
       <c r="B2">
-        <v>10.189036782993657</v>
+        <v>10.514936706909603</v>
       </c>
       <c r="C2">
         <v>237.49899054506031</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>4.8494979962866536</v>
+        <v>4.2396503317621308</v>
       </c>
       <c r="B3">
-        <v>9.9205715755918789</v>
+        <v>10.234299744202319</v>
       </c>
       <c r="C3">
         <v>237.49899054506031</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>4.1758106511003872</v>
+        <v>3.5590103458277795</v>
       </c>
       <c r="B4">
-        <v>9.6236729164256865</v>
+        <v>9.92168842799427</v>
       </c>
       <c r="C4">
         <v>237.49899054506031</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>3.5271573349144605</v>
+        <v>2.908860073198555</v>
       </c>
       <c r="B5">
-        <v>9.305187400850226</v>
+        <v>9.5853401695685978</v>
       </c>
       <c r="C5">
         <v>237.49899054506031</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>2.9002076520384388</v>
+        <v>2.2847892028635468</v>
       </c>
       <c r="B6">
-        <v>8.9679868308257156</v>
+        <v>9.2286884973609435</v>
       </c>
       <c r="C6">
         <v>237.49899054506031</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>2.2930063555982594</v>
+        <v>1.6842242619494594</v>
       </c>
       <c r="B7">
-        <v>8.6137572167628047</v>
+        <v>8.8537369191209763</v>
       </c>
       <c r="C7">
         <v>237.49899054506031</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>1.7043503664222015</v>
+        <v>1.10559687499673</v>
       </c>
       <c r="B8">
-        <v>8.2435359744657379</v>
+        <v>8.4617064511726827</v>
       </c>
       <c r="C8">
         <v>237.49899054506031</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>1.1324561468914891</v>
+        <v>0.5465557727966277</v>
       </c>
       <c r="B9">
-        <v>7.8588610493637843</v>
+        <v>8.054427610608407</v>
       </c>
       <c r="C9">
         <v>237.49899054506031</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>0.57541605920347461</v>
+        <v>0.0045809840073926175</v>
       </c>
       <c r="B10">
-        <v>7.4613773985401952</v>
+        <v>7.6338622530064821</v>
       </c>
       <c r="C10">
         <v>237.49899054506031</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>0.031406523267117015</v>
+        <v>-0.52273937749568522</v>
       </c>
       <c r="B11">
-        <v>7.0526574960691866</v>
+        <v>7.2018880871208335</v>
       </c>
       <c r="C11">
         <v>237.49899054506031</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-0.50058605214974106</v>
+        <v>-1.0367342828132</v>
       </c>
       <c r="B12">
-        <v>6.6335753622047875</v>
+        <v>6.7595397474823917</v>
       </c>
       <c r="C12">
         <v>237.49899054506031</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-1.0184193605553218</v>
+        <v>-1.5345091281663532</v>
       </c>
       <c r="B13">
-        <v>6.2022836849293475</v>
+        <v>6.3045637185545376</v>
       </c>
       <c r="C13">
         <v>237.49899054506031</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-1.5208379317041871</v>
+        <v>-2.01435935478283</v>
       </c>
       <c r="B14">
-        <v>5.757699871588116</v>
+        <v>5.8356329621759055</v>
       </c>
       <c r="C14">
         <v>237.49899054506031</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-2.0132895380601838</v>
+        <v>-2.4835641587956339</v>
       </c>
       <c r="B15">
-        <v>5.3045215392496825</v>
+        <v>5.3584144997537022</v>
       </c>
       <c r="C15">
         <v>237.49899054506031</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-2.5007703905724772</v>
+        <v>-2.9487995050228446</v>
       </c>
       <c r="B16">
-        <v>4.8470569232503831</v>
+        <v>4.8781057232590488</v>
       </c>
       <c r="C16">
         <v>237.49899054506031</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.9797672114222231</v>
+        <v>-3.4053446781175518</v>
       </c>
       <c r="B17">
-        <v>4.3822765222742142</v>
+        <v>4.3910314473501124</v>
       </c>
       <c r="C17">
         <v>237.49899054506031</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-3.4457227912832735</v>
+        <v>-3.8470825797232666</v>
       </c>
       <c r="B18">
-        <v>3.9062506523158906</v>
+        <v>3.8924293704344106</v>
       </c>
       <c r="C18">
         <v>237.49899054506031</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-3.8984136835683088</v>
+        <v>-4.2737072596102266</v>
       </c>
       <c r="B19">
-        <v>3.4187866352653273</v>
+        <v>3.3820613032297846</v>
       </c>
       <c r="C19">
         <v>237.49899054506031</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-4.3386998823747156</v>
+        <v>-4.6863655545803455</v>
       </c>
       <c r="B20">
-        <v>2.9206260444862364</v>
+        <v>2.8608200845316527</v>
       </c>
       <c r="C20">
         <v>237.49899054506031</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-4.7674413817998795</v>
+        <v>-5.0862043014355374</v>
       </c>
       <c r="B21">
-        <v>2.4125104533423349</v>
+        <v>2.32959855313544</v>
       </c>
       <c r="C21">
         <v>237.49899054506031</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-5.1853425403178068</v>
+        <v>-5.4741635502466464</v>
       </c>
       <c r="B22">
-        <v>1.8950472305172135</v>
+        <v>1.7891285596161206</v>
       </c>
       <c r="C22">
         <v>237.49899054506031</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-5.59248517390897</v>
+        <v>-5.8503562041602253</v>
       </c>
       <c r="B23">
-        <v>1.3683069259739837</v>
+        <v>1.2394980016668995</v>
       </c>
       <c r="C23">
         <v>237.49899054506031</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-5.9887954629304634</v>
+        <v>-6.2146883795917605</v>
       </c>
       <c r="B24">
-        <v>0.83222588499563821</v>
+        <v>0.68063378876053815</v>
       </c>
       <c r="C24">
         <v>237.49899054506031</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-6.3741995877393807</v>
+        <v>-6.56706619295673</v>
       </c>
       <c r="B25">
-        <v>0.2867404528651683</v>
+        <v>0.1124628303697966</v>
       </c>
       <c r="C25">
         <v>237.49899054506031</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-6.7485933991424352</v>
+        <v>-6.9073568290094292</v>
       </c>
       <c r="B26">
-        <v>-0.26823917832172106</v>
+        <v>-0.46511827322514088</v>
       </c>
       <c r="C26">
         <v>237.49899054506031</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-7.1117514297448459</v>
+        <v>-7.235271745859384</v>
       </c>
       <c r="B27">
-        <v>-0.83290742921846239</v>
+        <v>-1.0523341585143951</v>
       </c>
       <c r="C27">
         <v>237.49899054506031</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-7.463417882601445</v>
+        <v>-7.5504834699549255</v>
       </c>
       <c r="B28">
-        <v>-1.4074848736657653</v>
+        <v>-1.6494397711806537</v>
       </c>
       <c r="C28">
         <v>237.49899054506031</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-7.8033369607670711</v>
+        <v>-7.8526645277443938</v>
       </c>
       <c r="B29">
-        <v>-1.9921920855043509</v>
+        <v>-2.2566900569066131</v>
       </c>
       <c r="C29">
         <v>237.49899054506031</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-8.1313583701321761</v>
+        <v>-8.14163066762419</v>
       </c>
       <c r="B30">
-        <v>-2.5871586634241339</v>
+        <v>-2.8742284597982941</v>
       </c>
       <c r="C30">
         <v>237.49899054506031</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-8.4477538279296951</v>
+        <v>-8.4177705257830233</v>
       </c>
       <c r="B31">
-        <v>-3.1921503055118641</v>
+        <v>-3.5017524176550419</v>
       </c>
       <c r="C31">
         <v>237.49899054506031</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-8.7529005542281784</v>
+        <v>-8.6816159603576644</v>
       </c>
       <c r="B32">
-        <v>-3.8068417347034962</v>
+        <v>-4.1388478666995363</v>
       </c>
       <c r="C32">
         <v>237.49899054506031</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-9.0471757690961709</v>
+        <v>-8.9336988294849018</v>
       </c>
       <c r="B33">
-        <v>-4.4309076739349873</v>
+        <v>-4.7851007431544534</v>
       </c>
       <c r="C33">
         <v>237.49899054506031</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-9.3307682905494573</v>
+        <v>-9.1743009634702</v>
       </c>
       <c r="B34">
-        <v>-5.0641853053317458</v>
+        <v>-5.4402916356527644</v>
       </c>
       <c r="C34">
         <v>237.49899054506031</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-9.6031133283927463</v>
+        <v>-9.40270408129387</v>
       </c>
       <c r="B35">
-        <v>-5.70716164777703</v>
+        <v>-6.1049797424686663</v>
       </c>
       <c r="C35">
         <v>237.49899054506031</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-9.8634576903779738</v>
+        <v>-9.617939874104902</v>
       </c>
       <c r="B36">
-        <v>-6.3604861793435514</v>
+        <v>-6.7799189142866405</v>
       </c>
       <c r="C36">
         <v>237.49899054506031</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-10.11104818425709</v>
+        <v>-9.8190400330523051</v>
       </c>
       <c r="B37">
-        <v>-7.0248083781040318</v>
+        <v>-7.4658630017911864</v>
       </c>
       <c r="C37">
         <v>237.49899054506031</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-10.344680082476486</v>
+        <v>-10.0044339769924</v>
       </c>
       <c r="B38">
-        <v>-7.7011670812632751</v>
+        <v>-8.1640347384820338</v>
       </c>
       <c r="C38">
         <v>237.49899054506031</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-10.561342516260401</v>
+        <v>-10.170142035610809</v>
       </c>
       <c r="B39">
-        <v>-8.39215856255448</v>
+        <v>-8.8775323891199012</v>
       </c>
       <c r="C39">
         <v>237.49899054506031</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-10.757573081527534</v>
+        <v>-10.311582266300473</v>
       </c>
       <c r="B40">
-        <v>-9.1007684548429282</v>
+        <v>-9.6099231012807476</v>
       </c>
       <c r="C40">
         <v>237.49899054506031</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-10.929909374196582</v>
+        <v>-10.424172726454341</v>
       </c>
       <c r="B41">
-        <v>-9.8299823909939086</v>
+        <v>-10.364774022540534</v>
       </c>
       <c r="C41">
         <v>237.49899054506031</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-10.929909374196582</v>
+        <v>-10.424172726454341</v>
       </c>
       <c r="B42">
-        <v>-9.8299823909939086</v>
+        <v>-10.364774022540534</v>
       </c>
       <c r="C42">
         <v>237.49899054506031</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-10.602898363166341</v>
+        <v>-10.104379045090026</v>
       </c>
       <c r="B43">
-        <v>-9.2341445460571112</v>
+        <v>-9.7712355688647214</v>
       </c>
       <c r="C43">
         <v>237.49899054506031</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-10.278557239129272</v>
+        <v>-9.79132110770951</v>
       </c>
       <c r="B44">
-        <v>-8.6360044561580782</v>
+        <v>-9.172453183764036</v>
       </c>
       <c r="C44">
         <v>237.49899054506031</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-9.9538019481470119</v>
+        <v>-9.4808111807661444</v>
       </c>
       <c r="B45">
-        <v>-8.0382215026342969</v>
+        <v>-8.5716871140051367</v>
       </c>
       <c r="C45">
         <v>237.49899054506031</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-9.62554843628121</v>
+        <v>-9.168661530713285</v>
       </c>
       <c r="B46">
-        <v>-7.4434550668232706</v>
+        <v>-7.9721976063546958</v>
       </c>
       <c r="C46">
         <v>237.49899054506031</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-9.2911466685064621</v>
+        <v>-8.8512684456875981</v>
       </c>
       <c r="B47">
-        <v>-6.8539902753249491</v>
+        <v>-7.3767902332827671</v>
       </c>
       <c r="C47">
         <v>237.49899054506031</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-8.9496826854492149</v>
+        <v>-8.5273643005590074</v>
       </c>
       <c r="B48">
-        <v>-6.2706152357891574</v>
+        <v>-6.7864518700730034</v>
       </c>
       <c r="C48">
         <v>237.49899054506031</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-8.6006765466488613</v>
+        <v>-8.1962654918807409</v>
       </c>
       <c r="B49">
-        <v>-5.693743801128174</v>
+        <v>-6.2017147177124441</v>
       </c>
       <c r="C49">
         <v>237.49899054506031</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-8.2436483116448027</v>
+        <v>-7.8572884162060355</v>
       </c>
       <c r="B50">
-        <v>-5.1237898242542848</v>
+        <v>-5.6231109771881345</v>
       </c>
       <c r="C50">
         <v>237.49899054506031</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-7.8782906085376556</v>
+        <v>-7.5099830007515305</v>
       </c>
       <c r="B51">
-        <v>-4.5610183521184275</v>
+        <v>-5.0509910405009837</v>
       </c>
       <c r="C51">
         <v>237.49899054506031</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-7.5049863396729082</v>
+        <v>-7.1548332953875242</v>
       </c>
       <c r="B52">
-        <v>-4.00509920782616</v>
+        <v>-4.4849780637073842</v>
       </c>
       <c r="C52">
         <v>237.49899054506031</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-7.1242909759572575</v>
+        <v>-6.7925568806477195</v>
       </c>
       <c r="B53">
-        <v>-3.4555534085216908</v>
+        <v>-3.9245133938775876</v>
       </c>
       <c r="C53">
         <v>237.49899054506031</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-6.7367599882974121</v>
+        <v>-6.4238713370658163</v>
       </c>
       <c r="B54">
-        <v>-2.91190197134923</v>
+        <v>-3.3690383780818465</v>
       </c>
       <c r="C54">
         <v>237.49899054506031</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-6.3428306490938207</v>
+        <v>-6.0493377954053251</v>
       </c>
       <c r="B55">
-        <v>-2.3737678360872541</v>
+        <v>-2.8181161631304743</v>
       </c>
       <c r="C55">
         <v>237.49899054506031</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-5.9424674367219552</v>
+        <v>-5.6688915873489858</v>
       </c>
       <c r="B56">
-        <v>-1.8411816330513409</v>
+        <v>-2.271797094794024</v>
       </c>
       <c r="C56">
         <v>237.49899054506031</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-5.5355166310510278</v>
+        <v>-5.2823115948093395</v>
       </c>
       <c r="B57">
-        <v>-1.3142759151913239</v>
+        <v>-1.7302533185830993</v>
       </c>
       <c r="C57">
         <v>237.49899054506031</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-5.1218245119502637</v>
+        <v>-4.889376699698933</v>
       </c>
       <c r="B58">
-        <v>-0.79318323545704994</v>
+        <v>-1.1936569800083134</v>
       </c>
       <c r="C58">
         <v>237.49899054506031</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.7012562810472467</v>
+        <v>-4.4898928296306977</v>
       </c>
       <c r="B59">
-        <v>-0.27801983055613733</v>
+        <v>-0.66215916888122628</v>
       </c>
       <c r="C59">
         <v>237.49899054506031</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-4.273752827003034</v>
+        <v>-4.0837740950191224</v>
       </c>
       <c r="B60">
-        <v>0.23116332777267354</v>
+        <v>-0.13582675221721247</v>
       </c>
       <c r="C60">
         <v>237.49899054506031</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-3.839273960237056</v>
+        <v>-3.6709616519790829</v>
       </c>
       <c r="B61">
-        <v>0.7343315840328587</v>
+        <v>0.38529445866739748</v>
       </c>
       <c r="C61">
         <v>237.49899054506031</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-3.39777949116874</v>
+        <v>-3.2513966566254573</v>
       </c>
       <c r="B62">
-        <v>1.2314502827278961</v>
+        <v>0.90115865245627325</v>
       </c>
       <c r="C62">
         <v>237.49899054506031</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-2.9493734195516907</v>
+        <v>-2.8252151257325466</v>
       </c>
       <c r="B63">
-        <v>1.7226091029001631</v>
+        <v>1.4118717213327834</v>
       </c>
       <c r="C63">
         <v>237.49899054506031</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-2.4947365024762114</v>
+        <v>-2.3933325187123384</v>
       </c>
       <c r="B64">
-        <v>2.2083950617476469</v>
+        <v>1.9181463714790938</v>
       </c>
       <c r="C64">
         <v>237.49899054506031</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.0346936863667855</v>
+        <v>-1.9568591556362469</v>
       </c>
       <c r="B65">
-        <v>2.6895195110072287</v>
+        <v>2.4208470125770662</v>
       </c>
       <c r="C65">
         <v>237.49899054506031</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-1.5700699176478914</v>
+        <v>-1.5169053565756829</v>
       </c>
       <c r="B66">
-        <v>3.166693802415796</v>
+        <v>2.9208380543085664</v>
       </c>
       <c r="C66">
         <v>237.49899054506031</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.1005972754398283</v>
+        <v>-1.0731188328248973</v>
       </c>
       <c r="B67">
-        <v>3.6396869076574863</v>
+        <v>3.4178452318233914</v>
       </c>
       <c r="C67">
         <v>237.49899054506031</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-0.621636369646164</v>
+        <v>-0.61929686056949984</v>
       </c>
       <c r="B68">
-        <v>4.1044982782054529</v>
+        <v>3.9070395821430872</v>
       </c>
       <c r="C68">
         <v>237.49899054506031</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-0.12957780656259588</v>
+        <v>-0.1506185797854778</v>
       </c>
       <c r="B69">
-        <v>4.5580155319649807</v>
+        <v>4.3846679549941863</v>
       </c>
       <c r="C69">
         <v>237.49899054506031</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>0.37069635272990364</v>
+        <v>0.32635897928100405</v>
       </c>
       <c r="B70">
-        <v>5.0044484727808625</v>
+        <v>4.8558351490513987</v>
       </c>
       <c r="C70">
         <v>237.49899054506031</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>0.873863794823156</v>
+        <v>0.80448733829202634</v>
       </c>
       <c r="B71">
-        <v>5.4483865343118119</v>
+        <v>5.3261064189156144</v>
       </c>
       <c r="C71">
         <v>237.49899054506031</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>1.3813326517854159</v>
+        <v>1.2856301168128084</v>
       </c>
       <c r="B72">
-        <v>5.8886154835327664</v>
+        <v>5.7940308939442486</v>
       </c>
       <c r="C72">
         <v>237.49899054506031</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>1.8954115545740118</v>
+        <v>1.7728552147408623</v>
       </c>
       <c r="B73">
-        <v>6.3231445867517087</v>
+        <v>6.2572201435913009</v>
       </c>
       <c r="C73">
         <v>237.49899054506031</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>2.4152806842261305</v>
+        <v>2.2650355553997281</v>
       </c>
       <c r="B74">
-        <v>6.7526807742926227</v>
+        <v>6.7165516229405995</v>
       </c>
       <c r="C74">
         <v>237.49899054506031</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>2.9393246850075445</v>
+        <v>2.7599762049497318</v>
       </c>
       <c r="B75">
-        <v>7.1786169682570291</v>
+        <v>7.17373413840834</v>
       </c>
       <c r="C75">
         <v>237.49899054506031</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>3.4658745040185028</v>
+        <v>3.2554057774722942</v>
       </c>
       <c r="B76">
-        <v>7.6023923938406011</v>
+        <v>7.6305360161104092</v>
       </c>
       <c r="C76">
         <v>237.49899054506031</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>3.9934016939504731</v>
+        <v>3.7492387864295753</v>
       </c>
       <c r="B77">
-        <v>8.0253250319635434</v>
+        <v>8.0885808552243024</v>
       </c>
       <c r="C77">
         <v>237.49899054506031</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>4.5209939270253638</v>
+        <v>4.2402097948855726</v>
       </c>
       <c r="B78">
-        <v>8.4482015833500412</v>
+        <v>8.5488538274743089</v>
       </c>
       <c r="C78">
         <v>237.49899054506031</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>5.0470035786529239</v>
+        <v>4.7260658465406546</v>
       </c>
       <c r="B79">
-        <v>8.8724427955531855</v>
+        <v>9.0131089110945943</v>
       </c>
       <c r="C79">
         <v>237.49899054506031</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>5.568443616111562</v>
+        <v>5.2027543857484844</v>
       </c>
       <c r="B80">
-        <v>9.3006243884640867</v>
+        <v>9.4845011137511328</v>
       </c>
       <c r="C80">
         <v>237.49899054506031</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>6.0777472870264617</v>
+        <v>5.66008339978018</v>
       </c>
       <c r="B81">
-        <v>9.7392711766460422</v>
+        <v>9.97096515148423</v>
       </c>
       <c r="C81">
         <v>237.49899054506031</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>6.4355580523522447</v>
+        <v>5.911309418451733</v>
       </c>
       <c r="B82">
-        <v>10.308550377210825</v>
+        <v>10.617885105702456</v>
       </c>
       <c r="C82">
         <v>237.49899054506031</v>
